--- a/QRC improvements.xlsx
+++ b/QRC improvements.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30215"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5CE8C4ED-E359-4FEA-9B70-89B9239997DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E4A5A58-C59C-4487-804A-92F3958B3E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="32">
   <si>
     <t>QRC_v1</t>
   </si>
@@ -109,6 +109,15 @@
   </si>
   <si>
     <t>C-Swap gates with 6 control qubits</t>
+  </si>
+  <si>
+    <t>QRC_v1 cell count</t>
+  </si>
+  <si>
+    <t>QRC_v2 cell count</t>
+  </si>
+  <si>
+    <t>QRC_v3 cell count</t>
   </si>
   <si>
     <t>Binary</t>
@@ -1602,7 +1611,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>QRC_v1 qubits</c:v>
+                  <c:v>QRC_v1 cell count</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1689,7 +1698,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>QRC_v2 qubits</c:v>
+                  <c:v>QRC_v2 cell count</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1776,7 +1785,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>QRC_v3 qubits</c:v>
+                  <c:v>QRC_v3 cell count</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5003,13 +5012,13 @@
         <v>7</v>
       </c>
       <c r="T31" s="3" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="U31" s="3" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="V31" s="3" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="2:22">
@@ -5017,10 +5026,10 @@
         <v>3</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>2</v>
@@ -5200,7 +5209,7 @@
         <v>1</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>2</v>
@@ -5210,7 +5219,7 @@
         <v>1</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>2</v>
@@ -5220,7 +5229,7 @@
         <v>1</v>
       </c>
       <c r="N42" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>2</v>
@@ -5671,7 +5680,7 @@
         <v>1</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>2</v>
@@ -5681,7 +5690,7 @@
         <v>1</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J56" s="3" t="s">
         <v>2</v>
@@ -5691,7 +5700,7 @@
         <v>1</v>
       </c>
       <c r="N56" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="O56" s="3" t="s">
         <v>2</v>
